--- a/BASE_INICIATIVAS_PBB.xlsx
+++ b/BASE_INICIATIVAS_PBB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcidades.sharepoint.com/sites/DEREGSEMOB/Documentos Compartilhados/4. CGRM/6. PROGRAMA BICICLETA BRASIL/1. SELO BICICLETA BRASIL/0.BASE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramson/projetos-dev/painel_bicicleta_cgdi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="958" documentId="13_ncr:1_{B05AE031-623F-44DE-83BB-E1BAE0F14FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03D384F-D206-4212-8FA6-69DC8CF57BC2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5649375-3BE8-CB40-8D54-139AC2EAAA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2DED98F-172A-4CAE-8841-0765849278DE}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51140" windowHeight="21320" xr2:uid="{F2DED98F-172A-4CAE-8841-0765849278DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Iniciativas PBB" sheetId="26" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6096" uniqueCount="2683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6618" uniqueCount="2685">
   <si>
     <t>ID</t>
   </si>
@@ -8113,12 +8113,18 @@
   <si>
     <t>MDF (Movimento de Defesa das Favelas)</t>
   </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>PREMIADA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8743,7 +8749,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8921,6 +8927,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8968,7 +8977,29 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -9234,16 +9265,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -9267,23 +9288,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{469E017F-15A0-47C2-A1E3-80F1A128A23F}" name="Tabela143" displayName="Tabela143" ref="A2:N523" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A2:N523" xr:uid="{469E017F-15A0-47C2-A1E3-80F1A128A23F}"/>
-  <tableColumns count="14">
-    <tableColumn id="2" xr3:uid="{9363D36D-6546-43F8-85CA-F341E21B1881}" name="ID" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{9C5B0974-7864-4224-8AC0-D3BCFFEE93C6}" name="CERTIFICADO NO DRIVE?" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{9ED74C3E-D913-45FA-BA3C-2128118B3726}" name="PROPONENTE" dataDxfId="11"/>
-    <tableColumn id="28" xr3:uid="{D5AB59AC-98BC-423F-8D13-333572282335}" name="INICIATIVA" dataDxfId="10"/>
-    <tableColumn id="45" xr3:uid="{B486D8BF-F551-4989-947F-29EC12C4A370}" name="ESTADO DA APLICAÇÃO" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{54424C0E-B78A-42D3-8DFC-3A0DA6FA766A}" name=" DESCRIÇÃO" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{D888DAD8-6DEE-4FEE-B291-EA2607BB0342}" name="DATA DA CONCESSÃO DO SELO" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{A4A02B8A-0DAE-452D-AB63-DBF91EBEA85D}" name=" CATEGORIA" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{3F2FECE3-7E5C-460E-8549-E34139BE7834}" name=" INSTITUIÇÃO" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{8C9E716A-86E9-4143-B13F-18A656B7A981}" name="CÓDIGO IBGE" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{23E0CD7A-E381-4446-9866-69631ABC82DD}" name="MUNICÍPIO" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{4C3A186F-EAF2-403E-AFFC-D58A32ADE367}" name="UF" dataDxfId="2"/>
-    <tableColumn id="32" xr3:uid="{7E16EFBE-4F58-4039-8849-01A7EB21E889}" name="REGIÃO" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{3D41595C-EEFE-40EC-8E30-41BF76CBA362}" name="LINK DRIVE" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{469E017F-15A0-47C2-A1E3-80F1A128A23F}" name="Tabela143" displayName="Tabela143" ref="A2:O523" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A2:O523" xr:uid="{469E017F-15A0-47C2-A1E3-80F1A128A23F}"/>
+  <tableColumns count="15">
+    <tableColumn id="2" xr3:uid="{9363D36D-6546-43F8-85CA-F341E21B1881}" name="ID" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{9C5B0974-7864-4224-8AC0-D3BCFFEE93C6}" name="CERTIFICADO NO DRIVE?" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{9ED74C3E-D913-45FA-BA3C-2128118B3726}" name="PROPONENTE" dataDxfId="13"/>
+    <tableColumn id="28" xr3:uid="{D5AB59AC-98BC-423F-8D13-333572282335}" name="INICIATIVA" dataDxfId="12"/>
+    <tableColumn id="45" xr3:uid="{B486D8BF-F551-4989-947F-29EC12C4A370}" name="ESTADO DA APLICAÇÃO" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{54424C0E-B78A-42D3-8DFC-3A0DA6FA766A}" name=" DESCRIÇÃO" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{D888DAD8-6DEE-4FEE-B291-EA2607BB0342}" name="DATA DA CONCESSÃO DO SELO" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{A4A02B8A-0DAE-452D-AB63-DBF91EBEA85D}" name=" CATEGORIA" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{3F2FECE3-7E5C-460E-8549-E34139BE7834}" name=" INSTITUIÇÃO" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8C9E716A-86E9-4143-B13F-18A656B7A981}" name="CÓDIGO IBGE" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{23E0CD7A-E381-4446-9866-69631ABC82DD}" name="MUNICÍPIO" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{4C3A186F-EAF2-403E-AFFC-D58A32ADE367}" name="UF" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{7E16EFBE-4F58-4039-8849-01A7EB21E889}" name="REGIÃO" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{3D41595C-EEFE-40EC-8E30-41BF76CBA362}" name="LINK DRIVE" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{701B4850-3347-BE4B-9C80-7337F098430C}" name="PREMIADA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9606,26 +9628,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0BBFFE5-ABB9-41FB-B6F1-981EC0D9F991}">
-  <dimension ref="A2:N523"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24.75" customHeight="1"/>
+  <dimension ref="A2:O523"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="50" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="49.42578125" style="22" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="49.5" style="22" customWidth="1"/>
     <col min="7" max="7" width="38" style="8" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="24.5" style="8" customWidth="1"/>
     <col min="9" max="10" width="33" style="8" customWidth="1"/>
     <col min="11" max="12" width="14" style="8" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="9.1640625" style="8" customWidth="1"/>
     <col min="14" max="14" width="15" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.85546875" style="8" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="8"/>
+    <col min="15" max="15" width="59.83203125" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="24.75" customHeight="1">
+    <row r="2" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
@@ -9668,8 +9690,11 @@
       <c r="N2" s="12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O2" s="63" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>14</v>
       </c>
@@ -9712,8 +9737,11 @@
       <c r="N3" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O3" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="48" t="s">
         <v>26</v>
       </c>
@@ -9756,8 +9784,11 @@
       <c r="N4" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O4" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="48" t="s">
         <v>33</v>
       </c>
@@ -9800,8 +9831,11 @@
       <c r="N5" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O5" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="48" t="s">
         <v>43</v>
       </c>
@@ -9844,8 +9878,11 @@
       <c r="N6" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O6" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="48" t="s">
         <v>52</v>
       </c>
@@ -9888,8 +9925,11 @@
       <c r="N7" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O7" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="48" t="s">
         <v>63</v>
       </c>
@@ -9932,8 +9972,11 @@
       <c r="N8" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O8" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="48" t="s">
         <v>68</v>
       </c>
@@ -9976,8 +10019,11 @@
       <c r="N9" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O9" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="48" t="s">
         <v>76</v>
       </c>
@@ -10020,8 +10066,11 @@
       <c r="N10" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O10" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="48" t="s">
         <v>83</v>
       </c>
@@ -10064,8 +10113,11 @@
       <c r="N11" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O11" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="48" t="s">
         <v>89</v>
       </c>
@@ -10108,8 +10160,11 @@
       <c r="N12" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" s="29" customFormat="1" ht="24.75" customHeight="1">
+      <c r="O12" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="29" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="48" t="s">
         <v>96</v>
       </c>
@@ -10152,8 +10207,11 @@
       <c r="N13" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O13" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="48" t="s">
         <v>104</v>
       </c>
@@ -10196,8 +10254,11 @@
       <c r="N14" s="14" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O14" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="48" t="s">
         <v>110</v>
       </c>
@@ -10240,8 +10301,11 @@
       <c r="N15" s="14" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O15" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="48" t="s">
         <v>116</v>
       </c>
@@ -10284,8 +10348,11 @@
       <c r="N16" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O16" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="48" t="s">
         <v>122</v>
       </c>
@@ -10328,8 +10395,11 @@
       <c r="N17" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O17" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="48" t="s">
         <v>127</v>
       </c>
@@ -10372,8 +10442,11 @@
       <c r="N18" s="4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O18" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48" t="s">
         <v>134</v>
       </c>
@@ -10416,8 +10489,11 @@
       <c r="N19" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O19" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="48" t="s">
         <v>142</v>
       </c>
@@ -10460,8 +10536,11 @@
       <c r="N20" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O20" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="48" t="s">
         <v>147</v>
       </c>
@@ -10504,8 +10583,11 @@
       <c r="N21" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O21" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="48" t="s">
         <v>153</v>
       </c>
@@ -10548,8 +10630,11 @@
       <c r="N22" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O22" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="48" t="s">
         <v>159</v>
       </c>
@@ -10592,8 +10677,11 @@
       <c r="N23" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O23" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48" t="s">
         <v>165</v>
       </c>
@@ -10636,8 +10724,11 @@
       <c r="N24" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O24" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="48" t="s">
         <v>172</v>
       </c>
@@ -10680,8 +10771,11 @@
       <c r="N25" s="4" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O25" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="48" t="s">
         <v>179</v>
       </c>
@@ -10724,8 +10818,11 @@
       <c r="N26" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O26" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="48" t="s">
         <v>185</v>
       </c>
@@ -10768,8 +10865,11 @@
       <c r="N27" s="4" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O27" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="48" t="s">
         <v>191</v>
       </c>
@@ -10812,8 +10912,11 @@
       <c r="N28" s="14" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O28" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="48" t="s">
         <v>196</v>
       </c>
@@ -10856,8 +10959,11 @@
       <c r="N29" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O29" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="48" t="s">
         <v>203</v>
       </c>
@@ -10900,8 +11006,11 @@
       <c r="N30" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O30" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="48" t="s">
         <v>207</v>
       </c>
@@ -10944,8 +11053,11 @@
       <c r="N31" s="4" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O31" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="48" t="s">
         <v>214</v>
       </c>
@@ -10988,8 +11100,11 @@
       <c r="N32" s="4" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O32" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="48" t="s">
         <v>220</v>
       </c>
@@ -11032,8 +11147,11 @@
       <c r="N33" s="4" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O33" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48" t="s">
         <v>226</v>
       </c>
@@ -11076,8 +11194,11 @@
       <c r="N34" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O34" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="48" t="s">
         <v>231</v>
       </c>
@@ -11120,8 +11241,11 @@
       <c r="N35" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O35" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="48" t="s">
         <v>235</v>
       </c>
@@ -11164,8 +11288,11 @@
       <c r="N36" s="4" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O36" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="48" t="s">
         <v>241</v>
       </c>
@@ -11208,8 +11335,11 @@
       <c r="N37" s="4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O37" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="48" t="s">
         <v>246</v>
       </c>
@@ -11252,8 +11382,11 @@
       <c r="N38" s="4" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O38" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="48" t="s">
         <v>251</v>
       </c>
@@ -11296,8 +11429,11 @@
       <c r="N39" s="4" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O39" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="48" t="s">
         <v>256</v>
       </c>
@@ -11340,8 +11476,11 @@
       <c r="N40" s="14" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O40" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="48" t="s">
         <v>262</v>
       </c>
@@ -11384,8 +11523,11 @@
       <c r="N41" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O41" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="48" t="s">
         <v>268</v>
       </c>
@@ -11428,8 +11570,11 @@
       <c r="N42" s="2" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O42" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48" t="s">
         <v>273</v>
       </c>
@@ -11472,8 +11617,11 @@
       <c r="N43" s="2" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O43" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="48" t="s">
         <v>279</v>
       </c>
@@ -11516,8 +11664,11 @@
       <c r="N44" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O44" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="48" t="s">
         <v>286</v>
       </c>
@@ -11560,8 +11711,11 @@
       <c r="N45" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O45" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="48" t="s">
         <v>293</v>
       </c>
@@ -11604,8 +11758,11 @@
       <c r="N46" s="3" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O46" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="48" t="s">
         <v>299</v>
       </c>
@@ -11648,8 +11805,11 @@
       <c r="N47" s="3" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O47" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="48" t="s">
         <v>304</v>
       </c>
@@ -11692,8 +11852,11 @@
       <c r="N48" s="3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O48" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="48" t="s">
         <v>310</v>
       </c>
@@ -11736,8 +11899,11 @@
       <c r="N49" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O49" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="48" t="s">
         <v>317</v>
       </c>
@@ -11780,8 +11946,11 @@
       <c r="N50" s="3" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O50" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="48" t="s">
         <v>323</v>
       </c>
@@ -11824,8 +11993,11 @@
       <c r="N51" s="4" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O51" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="48" t="s">
         <v>329</v>
       </c>
@@ -11868,8 +12040,11 @@
       <c r="N52" s="4" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O52" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="48" t="s">
         <v>335</v>
       </c>
@@ -11912,8 +12087,11 @@
       <c r="N53" s="4" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O53" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="48" t="s">
         <v>341</v>
       </c>
@@ -11956,8 +12134,11 @@
       <c r="N54" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O54" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="48" t="s">
         <v>348</v>
       </c>
@@ -12000,8 +12181,11 @@
       <c r="N55" s="4" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O55" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="48" t="s">
         <v>354</v>
       </c>
@@ -12044,8 +12228,11 @@
       <c r="N56" s="3" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O56" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="48" t="s">
         <v>360</v>
       </c>
@@ -12088,8 +12275,11 @@
       <c r="N57" s="3" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O57" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="48" t="s">
         <v>366</v>
       </c>
@@ -12132,8 +12322,11 @@
       <c r="N58" s="4" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O58" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="48" t="s">
         <v>372</v>
       </c>
@@ -12176,8 +12369,11 @@
       <c r="N59" s="4" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O59" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="48" t="s">
         <v>378</v>
       </c>
@@ -12220,8 +12416,11 @@
       <c r="N60" s="3" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O60" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="48" t="s">
         <v>384</v>
       </c>
@@ -12264,8 +12463,11 @@
       <c r="N61" s="3" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O61" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="48" t="s">
         <v>391</v>
       </c>
@@ -12308,8 +12510,11 @@
       <c r="N62" s="3" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O62" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="48" t="s">
         <v>396</v>
       </c>
@@ -12352,8 +12557,11 @@
       <c r="N63" s="3" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O63" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="48" t="s">
         <v>400</v>
       </c>
@@ -12396,8 +12604,11 @@
       <c r="N64" s="3" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O64" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="48" t="s">
         <v>406</v>
       </c>
@@ -12440,8 +12651,11 @@
       <c r="N65" s="3" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O65" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="48" t="s">
         <v>410</v>
       </c>
@@ -12484,8 +12698,11 @@
       <c r="N66" s="4" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O66" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="48" t="s">
         <v>415</v>
       </c>
@@ -12528,8 +12745,11 @@
       <c r="N67" s="4" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O67" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="48" t="s">
         <v>420</v>
       </c>
@@ -12572,8 +12792,11 @@
       <c r="N68" s="4" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O68" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="48" t="s">
         <v>426</v>
       </c>
@@ -12616,8 +12839,11 @@
       <c r="N69" s="3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O69" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="48" t="s">
         <v>432</v>
       </c>
@@ -12660,8 +12886,11 @@
       <c r="N70" s="3" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O70" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="48" t="s">
         <v>437</v>
       </c>
@@ -12704,8 +12933,11 @@
       <c r="N71" s="3" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O71" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="48" t="s">
         <v>443</v>
       </c>
@@ -12748,8 +12980,11 @@
       <c r="N72" s="3" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O72" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="48" t="s">
         <v>449</v>
       </c>
@@ -12792,8 +13027,11 @@
       <c r="N73" s="4" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O73" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="48" t="s">
         <v>454</v>
       </c>
@@ -12836,8 +13074,11 @@
       <c r="N74" s="3" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O74" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="48" t="s">
         <v>460</v>
       </c>
@@ -12880,8 +13121,11 @@
       <c r="N75" s="3" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O75" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="48" t="s">
         <v>466</v>
       </c>
@@ -12924,8 +13168,11 @@
       <c r="N76" s="3" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O76" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="48" t="s">
         <v>472</v>
       </c>
@@ -12968,8 +13215,11 @@
       <c r="N77" s="3" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O77" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="48" t="s">
         <v>478</v>
       </c>
@@ -13012,8 +13262,11 @@
       <c r="N78" s="3" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O78" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="48" t="s">
         <v>483</v>
       </c>
@@ -13056,8 +13309,11 @@
       <c r="N79" s="3" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O79" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="48" t="s">
         <v>489</v>
       </c>
@@ -13100,8 +13356,11 @@
       <c r="N80" s="3" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O80" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="48" t="s">
         <v>495</v>
       </c>
@@ -13144,8 +13403,11 @@
       <c r="N81" s="3" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O81" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="48" t="s">
         <v>500</v>
       </c>
@@ -13188,8 +13450,11 @@
       <c r="N82" s="3" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O82" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="48" t="s">
         <v>505</v>
       </c>
@@ -13232,8 +13497,11 @@
       <c r="N83" s="3" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O83" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="48" t="s">
         <v>510</v>
       </c>
@@ -13276,8 +13544,11 @@
       <c r="N84" s="3" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O84" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="48" t="s">
         <v>516</v>
       </c>
@@ -13320,8 +13591,11 @@
       <c r="N85" s="3" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O85" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="48" t="s">
         <v>522</v>
       </c>
@@ -13364,8 +13638,11 @@
       <c r="N86" s="3" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O86" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="48" t="s">
         <v>526</v>
       </c>
@@ -13408,8 +13685,11 @@
       <c r="N87" s="3" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O87" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="48" t="s">
         <v>532</v>
       </c>
@@ -13452,8 +13732,11 @@
       <c r="N88" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O88" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="48" t="s">
         <v>536</v>
       </c>
@@ -13496,8 +13779,11 @@
       <c r="N89" s="3" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O89" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="48" t="s">
         <v>542</v>
       </c>
@@ -13540,8 +13826,11 @@
       <c r="N90" s="3" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O90" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="48" t="s">
         <v>548</v>
       </c>
@@ -13584,8 +13873,11 @@
       <c r="N91" s="3" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O91" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="48" t="s">
         <v>553</v>
       </c>
@@ -13628,8 +13920,11 @@
       <c r="N92" s="3" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O92" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="48" t="s">
         <v>558</v>
       </c>
@@ -13672,8 +13967,11 @@
       <c r="N93" s="3" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O93" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="48" t="s">
         <v>563</v>
       </c>
@@ -13716,8 +14014,11 @@
       <c r="N94" s="4" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O94" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="48" t="s">
         <v>568</v>
       </c>
@@ -13760,8 +14061,11 @@
       <c r="N95" s="3" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O95" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="48" t="s">
         <v>575</v>
       </c>
@@ -13804,8 +14108,11 @@
       <c r="N96" s="3" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O96" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="48" t="s">
         <v>581</v>
       </c>
@@ -13848,8 +14155,11 @@
       <c r="N97" s="35" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O97" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="48" t="s">
         <v>586</v>
       </c>
@@ -13892,8 +14202,11 @@
       <c r="N98" s="3" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O98" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="48" t="s">
         <v>592</v>
       </c>
@@ -13936,8 +14249,11 @@
       <c r="N99" s="35" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O99" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="48" t="s">
         <v>598</v>
       </c>
@@ -13980,8 +14296,11 @@
       <c r="N100" s="3" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O100" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="48" t="s">
         <v>604</v>
       </c>
@@ -14024,8 +14343,11 @@
       <c r="N101" s="35" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O101" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="48" t="s">
         <v>610</v>
       </c>
@@ -14068,8 +14390,11 @@
       <c r="N102" s="35" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O102" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="48" t="s">
         <v>616</v>
       </c>
@@ -14112,8 +14437,11 @@
       <c r="N103" s="35" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O103" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="48" t="s">
         <v>622</v>
       </c>
@@ -14156,8 +14484,11 @@
       <c r="N104" s="35" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O104" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="48" t="s">
         <v>628</v>
       </c>
@@ -14200,8 +14531,11 @@
       <c r="N105" s="3" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O105" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="48" t="s">
         <v>632</v>
       </c>
@@ -14244,8 +14578,11 @@
       <c r="N106" s="3" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O106" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="48" t="s">
         <v>636</v>
       </c>
@@ -14288,8 +14625,11 @@
       <c r="N107" s="3" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O107" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="48" t="s">
         <v>641</v>
       </c>
@@ -14332,8 +14672,11 @@
       <c r="N108" s="3" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O108" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="48" t="s">
         <v>645</v>
       </c>
@@ -14376,8 +14719,11 @@
       <c r="N109" s="3" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O109" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="48" t="s">
         <v>649</v>
       </c>
@@ -14420,8 +14766,11 @@
       <c r="N110" s="3" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O110" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="48" t="s">
         <v>654</v>
       </c>
@@ -14464,8 +14813,11 @@
       <c r="N111" s="4" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O111" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="48" t="s">
         <v>658</v>
       </c>
@@ -14508,8 +14860,11 @@
       <c r="N112" s="3" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O112" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="48" t="s">
         <v>663</v>
       </c>
@@ -14552,8 +14907,11 @@
       <c r="N113" s="3" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O113" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="48" t="s">
         <v>669</v>
       </c>
@@ -14596,8 +14954,11 @@
       <c r="N114" s="4" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O114" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="48" t="s">
         <v>676</v>
       </c>
@@ -14640,8 +15001,11 @@
       <c r="N115" s="4" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" s="29" customFormat="1" ht="24.75" customHeight="1">
+      <c r="O115" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" s="29" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="48" t="s">
         <v>680</v>
       </c>
@@ -14684,8 +15048,11 @@
       <c r="N116" s="3" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O116" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="48" t="s">
         <v>683</v>
       </c>
@@ -14728,8 +15095,11 @@
       <c r="N117" s="3" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O117" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="57" t="s">
         <v>689</v>
       </c>
@@ -14768,8 +15138,11 @@
         <v>61</v>
       </c>
       <c r="N118" s="10"/>
-    </row>
-    <row r="119" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O118" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="48" t="s">
         <v>696</v>
       </c>
@@ -14812,8 +15185,11 @@
       <c r="N119" s="3" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O119" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="48" t="s">
         <v>700</v>
       </c>
@@ -14856,8 +15232,11 @@
       <c r="N120" s="3" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O120" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="48" t="s">
         <v>706</v>
       </c>
@@ -14900,8 +15279,11 @@
       <c r="N121" s="3" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O121" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="48" t="s">
         <v>711</v>
       </c>
@@ -14944,8 +15326,11 @@
       <c r="N122" s="3" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O122" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="48" t="s">
         <v>717</v>
       </c>
@@ -14988,8 +15373,11 @@
       <c r="N123" s="3" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O123" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="48" t="s">
         <v>723</v>
       </c>
@@ -15032,8 +15420,11 @@
       <c r="N124" s="4" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O124" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="48" t="s">
         <v>729</v>
       </c>
@@ -15076,8 +15467,11 @@
       <c r="N125" s="3" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O125" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="48" t="s">
         <v>734</v>
       </c>
@@ -15120,8 +15514,11 @@
       <c r="N126" s="4" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O126" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="48" t="s">
         <v>739</v>
       </c>
@@ -15164,8 +15561,11 @@
       <c r="N127" s="4" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O127" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="48" t="s">
         <v>745</v>
       </c>
@@ -15208,8 +15608,11 @@
       <c r="N128" s="4" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O128" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="48" t="s">
         <v>749</v>
       </c>
@@ -15252,8 +15655,11 @@
       <c r="N129" s="4" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O129" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="48" t="s">
         <v>753</v>
       </c>
@@ -15296,8 +15702,11 @@
       <c r="N130" s="4" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O130" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="48" t="s">
         <v>757</v>
       </c>
@@ -15340,8 +15749,11 @@
       <c r="N131" s="4" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O131" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="48" t="s">
         <v>761</v>
       </c>
@@ -15384,8 +15796,11 @@
       <c r="N132" s="4" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O132" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="48" t="s">
         <v>767</v>
       </c>
@@ -15428,8 +15843,11 @@
       <c r="N133" s="3" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O133" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="48" t="s">
         <v>771</v>
       </c>
@@ -15472,8 +15890,11 @@
       <c r="N134" s="3" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O134" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="48" t="s">
         <v>777</v>
       </c>
@@ -15516,8 +15937,11 @@
       <c r="N135" s="3" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O135" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="48" t="s">
         <v>782</v>
       </c>
@@ -15560,8 +15984,11 @@
       <c r="N136" s="3" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O136" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="48" t="s">
         <v>787</v>
       </c>
@@ -15604,8 +16031,11 @@
       <c r="N137" s="4" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O137" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="48" t="s">
         <v>793</v>
       </c>
@@ -15648,8 +16078,11 @@
       <c r="N138" s="4" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O138" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="48" t="s">
         <v>798</v>
       </c>
@@ -15692,8 +16125,11 @@
       <c r="N139" s="4" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O139" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="57" t="s">
         <v>802</v>
       </c>
@@ -15732,8 +16168,11 @@
         <v>61</v>
       </c>
       <c r="N140" s="10"/>
-    </row>
-    <row r="141" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O140" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="48" t="s">
         <v>805</v>
       </c>
@@ -15776,8 +16215,11 @@
       <c r="N141" s="4" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O141" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="48" t="s">
         <v>811</v>
       </c>
@@ -15820,8 +16262,11 @@
       <c r="N142" s="35" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O142" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="48" t="s">
         <v>816</v>
       </c>
@@ -15864,8 +16309,11 @@
       <c r="N143" s="3" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O143" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="48" t="s">
         <v>821</v>
       </c>
@@ -15908,8 +16356,11 @@
       <c r="N144" s="3" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O144" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="48" t="s">
         <v>826</v>
       </c>
@@ -15952,8 +16403,11 @@
       <c r="N145" s="4" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O145" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="48" t="s">
         <v>832</v>
       </c>
@@ -15996,8 +16450,11 @@
       <c r="N146" s="4" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O146" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="48" t="s">
         <v>838</v>
       </c>
@@ -16040,8 +16497,11 @@
       <c r="N147" s="35" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O147" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="48" t="s">
         <v>844</v>
       </c>
@@ -16084,8 +16544,11 @@
       <c r="N148" s="3" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O148" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="48" t="s">
         <v>849</v>
       </c>
@@ -16128,8 +16591,11 @@
       <c r="N149" s="3" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O149" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="48" t="s">
         <v>855</v>
       </c>
@@ -16172,8 +16638,11 @@
       <c r="N150" s="4" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O150" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="48" t="s">
         <v>860</v>
       </c>
@@ -16216,8 +16685,11 @@
       <c r="N151" s="4" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O151" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="48" t="s">
         <v>864</v>
       </c>
@@ -16260,8 +16732,11 @@
       <c r="N152" s="4" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O152" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="48" t="s">
         <v>869</v>
       </c>
@@ -16304,8 +16779,11 @@
       <c r="N153" s="3" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O153" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="48" t="s">
         <v>875</v>
       </c>
@@ -16348,8 +16826,11 @@
       <c r="N154" s="4" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O154" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="48" t="s">
         <v>881</v>
       </c>
@@ -16392,8 +16873,11 @@
       <c r="N155" s="3" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O155" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="48" t="s">
         <v>887</v>
       </c>
@@ -16436,8 +16920,11 @@
       <c r="N156" s="3" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O156" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="48" t="s">
         <v>892</v>
       </c>
@@ -16480,8 +16967,11 @@
       <c r="N157" s="4" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O157" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="48" t="s">
         <v>898</v>
       </c>
@@ -16524,8 +17014,11 @@
       <c r="N158" s="3" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O158" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="48" t="s">
         <v>904</v>
       </c>
@@ -16568,8 +17061,11 @@
       <c r="N159" s="3" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O159" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="48" t="s">
         <v>908</v>
       </c>
@@ -16612,8 +17108,11 @@
       <c r="N160" s="3" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O160" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="48" t="s">
         <v>913</v>
       </c>
@@ -16656,8 +17155,11 @@
       <c r="N161" s="3" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O161" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="48" t="s">
         <v>919</v>
       </c>
@@ -16700,8 +17202,11 @@
       <c r="N162" s="3" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O162" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="48" t="s">
         <v>924</v>
       </c>
@@ -16744,8 +17249,11 @@
       <c r="N163" s="3" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O163" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="48" t="s">
         <v>927</v>
       </c>
@@ -16788,8 +17296,11 @@
       <c r="N164" s="3" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O164" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="48" t="s">
         <v>933</v>
       </c>
@@ -16832,8 +17343,11 @@
       <c r="N165" s="3" t="s">
         <v>937</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O165" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="48" t="s">
         <v>938</v>
       </c>
@@ -16876,8 +17390,11 @@
       <c r="N166" s="3" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O166" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="48" t="s">
         <v>944</v>
       </c>
@@ -16920,8 +17437,11 @@
       <c r="N167" s="4" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O167" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="48" t="s">
         <v>950</v>
       </c>
@@ -16964,8 +17484,11 @@
       <c r="N168" s="4" t="s">
         <v>954</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O168" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="48" t="s">
         <v>955</v>
       </c>
@@ -17008,8 +17531,11 @@
       <c r="N169" s="3" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O169" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="48" t="s">
         <v>961</v>
       </c>
@@ -17052,8 +17578,11 @@
       <c r="N170" s="3" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O170" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="48" t="s">
         <v>965</v>
       </c>
@@ -17096,8 +17625,11 @@
       <c r="N171" s="3" t="s">
         <v>970</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O171" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="48" t="s">
         <v>971</v>
       </c>
@@ -17140,8 +17672,11 @@
       <c r="N172" s="3" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O172" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="48" t="s">
         <v>978</v>
       </c>
@@ -17184,8 +17719,11 @@
       <c r="N173" s="3" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O173" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="48" t="s">
         <v>984</v>
       </c>
@@ -17228,8 +17766,11 @@
       <c r="N174" s="4" t="s">
         <v>989</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O174" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="48" t="s">
         <v>990</v>
       </c>
@@ -17272,8 +17813,11 @@
       <c r="N175" s="4" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O175" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="48" t="s">
         <v>996</v>
       </c>
@@ -17316,8 +17860,11 @@
       <c r="N176" s="4" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O176" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="48" t="s">
         <v>1002</v>
       </c>
@@ -17360,8 +17907,11 @@
       <c r="N177" s="4" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O177" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="48" t="s">
         <v>1007</v>
       </c>
@@ -17404,8 +17954,11 @@
       <c r="N178" s="3" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O178" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="48" t="s">
         <v>1014</v>
       </c>
@@ -17448,8 +18001,11 @@
       <c r="N179" s="4" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O179" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="48" t="s">
         <v>1019</v>
       </c>
@@ -17492,8 +18048,11 @@
       <c r="N180" s="4" t="s">
         <v>1024</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O180" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="48" t="s">
         <v>1025</v>
       </c>
@@ -17536,8 +18095,11 @@
       <c r="N181" s="3" t="s">
         <v>1030</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O181" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="48" t="s">
         <v>1031</v>
       </c>
@@ -17580,8 +18142,11 @@
       <c r="N182" s="3" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O182" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="48" t="s">
         <v>1036</v>
       </c>
@@ -17624,8 +18189,11 @@
       <c r="N183" s="4" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O183" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="48" t="s">
         <v>1042</v>
       </c>
@@ -17668,8 +18236,11 @@
       <c r="N184" s="4" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O184" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="48" t="s">
         <v>1047</v>
       </c>
@@ -17712,8 +18283,11 @@
       <c r="N185" s="4" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O185" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="48" t="s">
         <v>1051</v>
       </c>
@@ -17756,8 +18330,11 @@
       <c r="N186" s="3" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O186" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="48" t="s">
         <v>1056</v>
       </c>
@@ -17800,8 +18377,11 @@
       <c r="N187" s="3" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O187" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="48" t="s">
         <v>1062</v>
       </c>
@@ -17844,8 +18424,11 @@
       <c r="N188" s="3" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O188" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="48" t="s">
         <v>1067</v>
       </c>
@@ -17888,8 +18471,11 @@
       <c r="N189" s="3" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O189" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="48" t="s">
         <v>1072</v>
       </c>
@@ -17932,8 +18518,11 @@
       <c r="N190" s="4" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O190" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="48" t="s">
         <v>1078</v>
       </c>
@@ -17974,8 +18563,11 @@
       <c r="N191" s="3" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O191" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="48" t="s">
         <v>1084</v>
       </c>
@@ -18018,8 +18610,11 @@
       <c r="N192" s="3" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O192" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="48" t="s">
         <v>1089</v>
       </c>
@@ -18062,8 +18657,11 @@
       <c r="N193" s="4" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O193" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="48" t="s">
         <v>1094</v>
       </c>
@@ -18106,8 +18704,11 @@
       <c r="N194" s="3" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O194" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="48" t="s">
         <v>1099</v>
       </c>
@@ -18150,8 +18751,11 @@
       <c r="N195" s="3" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O195" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="48" t="s">
         <v>1104</v>
       </c>
@@ -18194,8 +18798,11 @@
       <c r="N196" s="3" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O196" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="48" t="s">
         <v>1109</v>
       </c>
@@ -18238,8 +18845,11 @@
       <c r="N197" s="4" t="s">
         <v>1112</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O197" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="48" t="s">
         <v>1113</v>
       </c>
@@ -18282,8 +18892,11 @@
       <c r="N198" s="4" t="s">
         <v>1116</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O198" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="48" t="s">
         <v>1117</v>
       </c>
@@ -18326,8 +18939,11 @@
       <c r="N199" s="4" t="s">
         <v>1120</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O199" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="48" t="s">
         <v>1121</v>
       </c>
@@ -18370,8 +18986,11 @@
       <c r="N200" s="4" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O200" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="48" t="s">
         <v>1126</v>
       </c>
@@ -18414,8 +19033,11 @@
       <c r="N201" s="4" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O201" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="48" t="s">
         <v>1130</v>
       </c>
@@ -18458,8 +19080,11 @@
       <c r="N202" s="4" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O202" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="48" t="s">
         <v>1134</v>
       </c>
@@ -18502,8 +19127,11 @@
       <c r="N203" s="4" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O203" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="48" t="s">
         <v>1140</v>
       </c>
@@ -18546,8 +19174,11 @@
       <c r="N204" s="4" t="s">
         <v>1144</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O204" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="48" t="s">
         <v>1145</v>
       </c>
@@ -18590,8 +19221,11 @@
       <c r="N205" s="3" t="s">
         <v>1148</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O205" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="48" t="s">
         <v>1149</v>
       </c>
@@ -18634,8 +19268,11 @@
       <c r="N206" s="4" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O206" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="48" t="s">
         <v>1153</v>
       </c>
@@ -18678,8 +19315,11 @@
       <c r="N207" s="4" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O207" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="48" t="s">
         <v>1157</v>
       </c>
@@ -18722,8 +19362,11 @@
       <c r="N208" s="4" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O208" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="48" t="s">
         <v>1162</v>
       </c>
@@ -18766,8 +19409,11 @@
       <c r="N209" s="3" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O209" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="48" t="s">
         <v>1167</v>
       </c>
@@ -18810,8 +19456,11 @@
       <c r="N210" s="3" t="s">
         <v>1172</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O210" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="48" t="s">
         <v>1173</v>
       </c>
@@ -18854,8 +19503,11 @@
       <c r="N211" s="3" t="s">
         <v>1177</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O211" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="48" t="s">
         <v>1178</v>
       </c>
@@ -18898,8 +19550,11 @@
       <c r="N212" s="4" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O212" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="48" t="s">
         <v>1183</v>
       </c>
@@ -18942,8 +19597,11 @@
       <c r="N213" s="3" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O213" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="48" t="s">
         <v>1189</v>
       </c>
@@ -18986,8 +19644,11 @@
       <c r="N214" s="4" t="s">
         <v>1194</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O214" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="48" t="s">
         <v>1195</v>
       </c>
@@ -19030,8 +19691,11 @@
       <c r="N215" s="4" t="s">
         <v>1198</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O215" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="48" t="s">
         <v>1199</v>
       </c>
@@ -19074,8 +19738,11 @@
       <c r="N216" s="3" t="s">
         <v>1204</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O216" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="48" t="s">
         <v>1205</v>
       </c>
@@ -19118,8 +19785,11 @@
       <c r="N217" s="4" t="s">
         <v>1210</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O217" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="48" t="s">
         <v>1211</v>
       </c>
@@ -19162,8 +19832,11 @@
       <c r="N218" s="3" t="s">
         <v>1215</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O218" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="48" t="s">
         <v>1216</v>
       </c>
@@ -19206,8 +19879,11 @@
       <c r="N219" s="4" t="s">
         <v>1221</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O219" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="48" t="s">
         <v>1222</v>
       </c>
@@ -19250,8 +19926,11 @@
       <c r="N220" s="4" t="s">
         <v>1225</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O220" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="48" t="s">
         <v>1226</v>
       </c>
@@ -19294,8 +19973,11 @@
       <c r="N221" s="3" t="s">
         <v>1229</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O221" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="48" t="s">
         <v>1230</v>
       </c>
@@ -19338,8 +20020,11 @@
       <c r="N222" s="4" t="s">
         <v>1234</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O222" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="48" t="s">
         <v>1235</v>
       </c>
@@ -19382,8 +20067,11 @@
       <c r="N223" s="4" t="s">
         <v>1239</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O223" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="48" t="s">
         <v>1240</v>
       </c>
@@ -19426,8 +20114,11 @@
       <c r="N224" s="3" t="s">
         <v>1244</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O224" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="48" t="s">
         <v>1245</v>
       </c>
@@ -19470,8 +20161,11 @@
       <c r="N225" s="4" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O225" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="48" t="s">
         <v>1250</v>
       </c>
@@ -19514,8 +20208,11 @@
       <c r="N226" s="4" t="s">
         <v>1253</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O226" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="48" t="s">
         <v>1254</v>
       </c>
@@ -19558,8 +20255,11 @@
       <c r="N227" s="4" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O227" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="48" t="s">
         <v>1260</v>
       </c>
@@ -19602,8 +20302,11 @@
       <c r="N228" s="4" t="s">
         <v>1264</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O228" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="48" t="s">
         <v>1265</v>
       </c>
@@ -19646,8 +20349,11 @@
       <c r="N229" s="3" t="s">
         <v>1268</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" s="29" customFormat="1" ht="24.75" customHeight="1">
+      <c r="O229" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" s="29" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="48" t="s">
         <v>1269</v>
       </c>
@@ -19690,8 +20396,11 @@
       <c r="N230" s="4" t="s">
         <v>1273</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O230" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="48" t="s">
         <v>1274</v>
       </c>
@@ -19734,8 +20443,11 @@
       <c r="N231" s="4" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O231" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="48" t="s">
         <v>1279</v>
       </c>
@@ -19778,8 +20490,11 @@
       <c r="N232" s="3" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O232" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="48" t="s">
         <v>1283</v>
       </c>
@@ -19822,8 +20537,11 @@
       <c r="N233" s="3" t="s">
         <v>1287</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O233" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="48" t="s">
         <v>1288</v>
       </c>
@@ -19866,8 +20584,11 @@
       <c r="N234" s="4" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O234" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="48" t="s">
         <v>1293</v>
       </c>
@@ -19910,8 +20631,11 @@
       <c r="N235" s="4" t="s">
         <v>1298</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O235" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="48" t="s">
         <v>1299</v>
       </c>
@@ -19954,8 +20678,11 @@
       <c r="N236" s="4" t="s">
         <v>1304</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O236" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="48" t="s">
         <v>1305</v>
       </c>
@@ -19998,8 +20725,11 @@
       <c r="N237" s="3" t="s">
         <v>1309</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O237" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="48" t="s">
         <v>1310</v>
       </c>
@@ -20042,8 +20772,11 @@
       <c r="N238" s="4" t="s">
         <v>1314</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O238" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="48" t="s">
         <v>1315</v>
       </c>
@@ -20086,8 +20819,11 @@
       <c r="N239" s="4" t="s">
         <v>1319</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O239" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="48" t="s">
         <v>1320</v>
       </c>
@@ -20130,8 +20866,11 @@
       <c r="N240" s="4" t="s">
         <v>1325</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O240" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="48" t="s">
         <v>1326</v>
       </c>
@@ -20174,8 +20913,11 @@
       <c r="N241" s="4" t="s">
         <v>1330</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O241" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="48" t="s">
         <v>1331</v>
       </c>
@@ -20218,8 +20960,11 @@
       <c r="N242" s="4" t="s">
         <v>1335</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O242" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="57" t="s">
         <v>1336</v>
       </c>
@@ -20258,8 +21003,11 @@
         <v>140</v>
       </c>
       <c r="N243" s="10"/>
-    </row>
-    <row r="244" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O243" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="48" t="s">
         <v>1342</v>
       </c>
@@ -20302,8 +21050,11 @@
       <c r="N244" s="4" t="s">
         <v>1347</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O244" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="48" t="s">
         <v>1348</v>
       </c>
@@ -20346,8 +21097,11 @@
       <c r="N245" s="4" t="s">
         <v>1352</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O245" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="48" t="s">
         <v>1353</v>
       </c>
@@ -20390,8 +21144,11 @@
       <c r="N246" s="4" t="s">
         <v>1356</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O246" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="48" t="s">
         <v>1357</v>
       </c>
@@ -20434,8 +21191,11 @@
       <c r="N247" s="4" t="s">
         <v>1362</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O247" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="48" t="s">
         <v>1363</v>
       </c>
@@ -20478,8 +21238,11 @@
       <c r="N248" s="4" t="s">
         <v>1368</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O248" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="48" t="s">
         <v>1369</v>
       </c>
@@ -20522,8 +21285,11 @@
       <c r="N249" s="3" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O249" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="48" t="s">
         <v>1374</v>
       </c>
@@ -20566,8 +21332,11 @@
       <c r="N250" s="3" t="s">
         <v>1379</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O250" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="48" t="s">
         <v>1380</v>
       </c>
@@ -20610,8 +21379,11 @@
       <c r="N251" s="4" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O251" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="48" t="s">
         <v>1385</v>
       </c>
@@ -20654,8 +21426,11 @@
       <c r="N252" s="3" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O252" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="48" t="s">
         <v>1391</v>
       </c>
@@ -20698,8 +21473,11 @@
       <c r="N253" s="4" t="s">
         <v>1396</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O253" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="48" t="s">
         <v>1397</v>
       </c>
@@ -20742,8 +21520,11 @@
       <c r="N254" s="4" t="s">
         <v>1401</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O254" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="48" t="s">
         <v>1402</v>
       </c>
@@ -20786,8 +21567,11 @@
       <c r="N255" s="4" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O255" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="48" t="s">
         <v>1407</v>
       </c>
@@ -20830,8 +21614,11 @@
       <c r="N256" s="3" t="s">
         <v>1412</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O256" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="48" t="s">
         <v>1413</v>
       </c>
@@ -20874,8 +21661,11 @@
       <c r="N257" s="4" t="s">
         <v>1418</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O257" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="48" t="s">
         <v>1419</v>
       </c>
@@ -20918,8 +21708,11 @@
       <c r="N258" s="4" t="s">
         <v>1424</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O258" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="48" t="s">
         <v>1425</v>
       </c>
@@ -20962,8 +21755,11 @@
       <c r="N259" s="4" t="s">
         <v>1429</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O259" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="48" t="s">
         <v>1430</v>
       </c>
@@ -21006,8 +21802,11 @@
       <c r="N260" s="4" t="s">
         <v>1436</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O260" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="48" t="s">
         <v>1437</v>
       </c>
@@ -21050,8 +21849,11 @@
       <c r="N261" s="4" t="s">
         <v>1442</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O261" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="48" t="s">
         <v>1443</v>
       </c>
@@ -21094,8 +21896,11 @@
       <c r="N262" s="3" t="s">
         <v>1447</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O262" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="48" t="s">
         <v>1448</v>
       </c>
@@ -21138,8 +21943,11 @@
       <c r="N263" s="4" t="s">
         <v>1453</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O263" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="48" t="s">
         <v>1454</v>
       </c>
@@ -21182,8 +21990,11 @@
       <c r="N264" s="4" t="s">
         <v>1459</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O264" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="48" t="s">
         <v>1460</v>
       </c>
@@ -21226,8 +22037,11 @@
       <c r="N265" s="4" t="s">
         <v>1466</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O265" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="48" t="s">
         <v>1467</v>
       </c>
@@ -21270,8 +22084,11 @@
       <c r="N266" s="4" t="s">
         <v>1471</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O266" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="48" t="s">
         <v>1472</v>
       </c>
@@ -21314,8 +22131,11 @@
       <c r="N267" s="4" t="s">
         <v>1477</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" s="29" customFormat="1" ht="24.75" customHeight="1">
+      <c r="O267" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" s="29" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="48" t="s">
         <v>1478</v>
       </c>
@@ -21358,8 +22178,11 @@
       <c r="N268" s="4" t="s">
         <v>1483</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O268" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="48" t="s">
         <v>1484</v>
       </c>
@@ -21402,8 +22225,11 @@
       <c r="N269" s="4" t="s">
         <v>1487</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O269" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="48" t="s">
         <v>1488</v>
       </c>
@@ -21446,8 +22272,11 @@
       <c r="N270" s="4" t="s">
         <v>1493</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O270" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="48" t="s">
         <v>1494</v>
       </c>
@@ -21490,8 +22319,11 @@
       <c r="N271" s="4" t="s">
         <v>1499</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O271" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="48" t="s">
         <v>1500</v>
       </c>
@@ -21534,8 +22366,11 @@
       <c r="N272" s="4" t="s">
         <v>1503</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O272" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="48" t="s">
         <v>1504</v>
       </c>
@@ -21578,8 +22413,11 @@
       <c r="N273" s="4" t="s">
         <v>1508</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O273" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="48" t="s">
         <v>1509</v>
       </c>
@@ -21622,8 +22460,11 @@
       <c r="N274" s="4" t="s">
         <v>1514</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O274" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="48" t="s">
         <v>1515</v>
       </c>
@@ -21666,8 +22507,11 @@
       <c r="N275" s="4" t="s">
         <v>1520</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O275" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="48" t="s">
         <v>1521</v>
       </c>
@@ -21710,8 +22554,11 @@
       <c r="N276" s="4" t="s">
         <v>1526</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O276" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="48" t="s">
         <v>1527</v>
       </c>
@@ -21754,8 +22601,11 @@
       <c r="N277" s="3" t="s">
         <v>1532</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O277" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="48" t="s">
         <v>1533</v>
       </c>
@@ -21798,8 +22648,11 @@
       <c r="N278" s="4" t="s">
         <v>1538</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O278" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="48" t="s">
         <v>1539</v>
       </c>
@@ -21842,8 +22695,11 @@
       <c r="N279" s="4" t="s">
         <v>1543</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O279" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="48" t="s">
         <v>1544</v>
       </c>
@@ -21886,8 +22742,11 @@
       <c r="N280" s="4" t="s">
         <v>1549</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O280" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="48" t="s">
         <v>1550</v>
       </c>
@@ -21930,8 +22789,11 @@
       <c r="N281" s="4" t="s">
         <v>1554</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O281" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="48" t="s">
         <v>1555</v>
       </c>
@@ -21974,8 +22836,11 @@
       <c r="N282" s="3" t="s">
         <v>1559</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O282" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="48" t="s">
         <v>1560</v>
       </c>
@@ -22018,8 +22883,11 @@
       <c r="N283" s="3" t="s">
         <v>1564</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O283" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="48" t="s">
         <v>1565</v>
       </c>
@@ -22062,8 +22930,11 @@
       <c r="N284" s="4" t="s">
         <v>1569</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O284" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="48" t="s">
         <v>1570</v>
       </c>
@@ -22106,8 +22977,11 @@
       <c r="N285" s="4" t="s">
         <v>1574</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O285" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="48" t="s">
         <v>1575</v>
       </c>
@@ -22150,8 +23024,11 @@
       <c r="N286" s="3" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O286" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="48" t="s">
         <v>1579</v>
       </c>
@@ -22194,8 +23071,11 @@
       <c r="N287" s="3" t="s">
         <v>1582</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O287" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="48" t="s">
         <v>1583</v>
       </c>
@@ -22238,8 +23118,11 @@
       <c r="N288" s="3" t="s">
         <v>1588</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O288" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="48" t="s">
         <v>1589</v>
       </c>
@@ -22282,8 +23165,11 @@
       <c r="N289" s="3" t="s">
         <v>1594</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O289" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="48" t="s">
         <v>1595</v>
       </c>
@@ -22326,8 +23212,11 @@
       <c r="N290" s="4" t="s">
         <v>1599</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O290" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="48" t="s">
         <v>1600</v>
       </c>
@@ -22370,8 +23259,11 @@
       <c r="N291" s="4" t="s">
         <v>1603</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O291" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="48" t="s">
         <v>1604</v>
       </c>
@@ -22414,8 +23306,11 @@
       <c r="N292" s="3" t="s">
         <v>1609</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O292" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="48" t="s">
         <v>1610</v>
       </c>
@@ -22458,8 +23353,11 @@
       <c r="N293" s="3" t="s">
         <v>1613</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O293" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="48" t="s">
         <v>1614</v>
       </c>
@@ -22502,8 +23400,11 @@
       <c r="N294" s="3" t="s">
         <v>1619</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O294" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="48" t="s">
         <v>1620</v>
       </c>
@@ -22546,8 +23447,11 @@
       <c r="N295" s="4" t="s">
         <v>1624</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O295" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="48" t="s">
         <v>1625</v>
       </c>
@@ -22590,8 +23494,11 @@
       <c r="N296" s="4" t="s">
         <v>1630</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O296" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="48" t="s">
         <v>1631</v>
       </c>
@@ -22634,8 +23541,11 @@
       <c r="N297" s="4" t="s">
         <v>1624</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O297" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="48" t="s">
         <v>1635</v>
       </c>
@@ -22678,8 +23588,11 @@
       <c r="N298" s="3" t="s">
         <v>1638</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O298" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="48" t="s">
         <v>1639</v>
       </c>
@@ -22722,8 +23635,11 @@
       <c r="N299" s="4" t="s">
         <v>1643</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O299" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="48" t="s">
         <v>1644</v>
       </c>
@@ -22766,8 +23682,11 @@
       <c r="N300" s="4" t="s">
         <v>1624</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O300" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="48" t="s">
         <v>1647</v>
       </c>
@@ -22810,8 +23729,11 @@
       <c r="N301" s="4" t="s">
         <v>1532</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O301" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="48" t="s">
         <v>1650</v>
       </c>
@@ -22854,8 +23776,11 @@
       <c r="N302" s="4" t="s">
         <v>1655</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O302" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="48" t="s">
         <v>1656</v>
       </c>
@@ -22898,8 +23823,11 @@
       <c r="N303" s="4" t="s">
         <v>1661</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O303" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="48" t="s">
         <v>1662</v>
       </c>
@@ -22942,8 +23870,11 @@
       <c r="N304" s="4" t="s">
         <v>1666</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O304" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="48" t="s">
         <v>1667</v>
       </c>
@@ -22986,8 +23917,11 @@
       <c r="N305" s="4" t="s">
         <v>1670</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O305" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="48" t="s">
         <v>1671</v>
       </c>
@@ -23030,8 +23964,11 @@
       <c r="N306" s="4" t="s">
         <v>1675</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O306" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="48" t="s">
         <v>1676</v>
       </c>
@@ -23074,8 +24011,11 @@
       <c r="N307" s="4" t="s">
         <v>1682</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O307" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="48" t="s">
         <v>1683</v>
       </c>
@@ -23118,8 +24058,11 @@
       <c r="N308" s="4" t="s">
         <v>1690</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O308" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="48" t="s">
         <v>1691</v>
       </c>
@@ -23162,8 +24105,11 @@
       <c r="N309" s="3" t="s">
         <v>1696</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O309" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="48" t="s">
         <v>1697</v>
       </c>
@@ -23206,8 +24152,11 @@
       <c r="N310" s="4" t="s">
         <v>1702</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O310" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="48" t="s">
         <v>1703</v>
       </c>
@@ -23250,8 +24199,11 @@
       <c r="N311" s="4" t="s">
         <v>1708</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O311" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="48" t="s">
         <v>1709</v>
       </c>
@@ -23294,8 +24246,11 @@
       <c r="N312" s="4" t="s">
         <v>1714</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O312" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="48" t="s">
         <v>1715</v>
       </c>
@@ -23338,8 +24293,11 @@
       <c r="N313" s="3" t="s">
         <v>1720</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O313" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="48" t="s">
         <v>1721</v>
       </c>
@@ -23382,8 +24340,11 @@
       <c r="N314" s="4" t="s">
         <v>1725</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O314" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="48" t="s">
         <v>1726</v>
       </c>
@@ -23426,8 +24387,11 @@
       <c r="N315" s="4" t="s">
         <v>1730</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O315" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="48" t="s">
         <v>1731</v>
       </c>
@@ -23470,8 +24434,11 @@
       <c r="N316" s="3" t="s">
         <v>1696</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O316" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="48" t="s">
         <v>1735</v>
       </c>
@@ -23514,8 +24481,11 @@
       <c r="N317" s="4" t="s">
         <v>1738</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O317" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="48" t="s">
         <v>1739</v>
       </c>
@@ -23558,8 +24528,11 @@
       <c r="N318" s="3" t="s">
         <v>1744</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O318" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="48" t="s">
         <v>1745</v>
       </c>
@@ -23602,8 +24575,11 @@
       <c r="N319" s="4" t="s">
         <v>1750</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O319" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="48" t="s">
         <v>1751</v>
       </c>
@@ -23646,8 +24622,11 @@
       <c r="N320" s="4" t="s">
         <v>1756</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O320" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="48" t="s">
         <v>1757</v>
       </c>
@@ -23690,8 +24669,11 @@
       <c r="N321" s="3" t="s">
         <v>1762</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O321" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="48" t="s">
         <v>1763</v>
       </c>
@@ -23734,8 +24716,11 @@
       <c r="N322" s="3" t="s">
         <v>1768</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O322" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="48" t="s">
         <v>1769</v>
       </c>
@@ -23778,8 +24763,11 @@
       <c r="N323" s="3" t="s">
         <v>1619</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O323" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="48" t="s">
         <v>1774</v>
       </c>
@@ -23822,8 +24810,11 @@
       <c r="N324" s="4" t="s">
         <v>1779</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O324" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="48" t="s">
         <v>1780</v>
       </c>
@@ -23866,8 +24857,11 @@
       <c r="N325" s="4" t="s">
         <v>1785</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O325" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="48" t="s">
         <v>1786</v>
       </c>
@@ -23910,8 +24904,11 @@
       <c r="N326" s="4" t="s">
         <v>1791</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O326" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="48" t="s">
         <v>1792</v>
       </c>
@@ -23954,8 +24951,11 @@
       <c r="N327" s="3" t="s">
         <v>1797</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O327" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="48" t="s">
         <v>1798</v>
       </c>
@@ -23998,8 +24998,11 @@
       <c r="N328" s="3" t="s">
         <v>1802</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O328" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="48" t="s">
         <v>1803</v>
       </c>
@@ -24042,8 +25045,11 @@
       <c r="N329" s="3" t="s">
         <v>1807</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O329" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="48" t="s">
         <v>1808</v>
       </c>
@@ -24086,8 +25092,11 @@
       <c r="N330" s="4" t="s">
         <v>1813</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O330" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="48" t="s">
         <v>1814</v>
       </c>
@@ -24130,8 +25139,11 @@
       <c r="N331" s="4" t="s">
         <v>1819</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O331" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="48" t="s">
         <v>1820</v>
       </c>
@@ -24174,8 +25186,11 @@
       <c r="N332" s="4" t="s">
         <v>1826</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O332" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="48" t="s">
         <v>1827</v>
       </c>
@@ -24218,8 +25233,11 @@
       <c r="N333" s="4" t="s">
         <v>1832</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O333" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="48" t="s">
         <v>1833</v>
       </c>
@@ -24262,8 +25280,11 @@
       <c r="N334" s="3" t="s">
         <v>1838</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O334" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="48" t="s">
         <v>1839</v>
       </c>
@@ -24306,8 +25327,11 @@
       <c r="N335" s="4" t="s">
         <v>1842</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O335" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="48" t="s">
         <v>1843</v>
       </c>
@@ -24350,8 +25374,11 @@
       <c r="N336" s="4" t="s">
         <v>1846</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O336" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="48" t="s">
         <v>1847</v>
       </c>
@@ -24394,8 +25421,11 @@
       <c r="N337" s="4" t="s">
         <v>1850</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O337" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="48" t="s">
         <v>1851</v>
       </c>
@@ -24438,8 +25468,11 @@
       <c r="N338" s="3" t="s">
         <v>1854</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O338" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="48" t="s">
         <v>1855</v>
       </c>
@@ -24482,8 +25515,11 @@
       <c r="N339" s="4" t="s">
         <v>1860</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O339" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="48" t="s">
         <v>1861</v>
       </c>
@@ -24526,8 +25562,11 @@
       <c r="N340" s="3" t="s">
         <v>1866</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O340" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="48" t="s">
         <v>1867</v>
       </c>
@@ -24570,8 +25609,11 @@
       <c r="N341" s="3" t="s">
         <v>1872</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O341" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="48" t="s">
         <v>1873</v>
       </c>
@@ -24614,8 +25656,11 @@
       <c r="N342" s="3" t="s">
         <v>1877</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O342" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="48" t="s">
         <v>1878</v>
       </c>
@@ -24658,8 +25703,11 @@
       <c r="N343" s="3" t="s">
         <v>1883</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O343" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="48" t="s">
         <v>1884</v>
       </c>
@@ -24702,8 +25750,11 @@
       <c r="N344" s="3" t="s">
         <v>1889</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O344" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="48" t="s">
         <v>1890</v>
       </c>
@@ -24746,8 +25797,11 @@
       <c r="N345" s="3" t="s">
         <v>1894</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O345" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="48" t="s">
         <v>1895</v>
       </c>
@@ -24790,8 +25844,11 @@
       <c r="N346" s="4" t="s">
         <v>1900</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O346" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="48" t="s">
         <v>1901</v>
       </c>
@@ -24834,8 +25891,11 @@
       <c r="N347" s="4" t="s">
         <v>1906</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O347" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="48" t="s">
         <v>1907</v>
       </c>
@@ -24878,8 +25938,11 @@
       <c r="N348" s="4" t="s">
         <v>1912</v>
       </c>
-    </row>
-    <row r="349" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O348" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="48" t="s">
         <v>1913</v>
       </c>
@@ -24922,8 +25985,11 @@
       <c r="N349" s="3" t="s">
         <v>1918</v>
       </c>
-    </row>
-    <row r="350" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O349" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="48" t="s">
         <v>1919</v>
       </c>
@@ -24966,8 +26032,11 @@
       <c r="N350" s="3" t="s">
         <v>1923</v>
       </c>
-    </row>
-    <row r="351" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O350" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="48" t="s">
         <v>1924</v>
       </c>
@@ -25010,8 +26079,11 @@
       <c r="N351" s="3" t="s">
         <v>1929</v>
       </c>
-    </row>
-    <row r="352" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O351" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="48" t="s">
         <v>1930</v>
       </c>
@@ -25054,8 +26126,11 @@
       <c r="N352" s="4" t="s">
         <v>1934</v>
       </c>
-    </row>
-    <row r="353" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O352" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="48" t="s">
         <v>1935</v>
       </c>
@@ -25098,8 +26173,11 @@
       <c r="N353" s="4" t="s">
         <v>1940</v>
       </c>
-    </row>
-    <row r="354" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O353" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="48" t="s">
         <v>1941</v>
       </c>
@@ -25142,8 +26220,11 @@
       <c r="N354" s="4" t="s">
         <v>1946</v>
       </c>
-    </row>
-    <row r="355" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O354" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="48" t="s">
         <v>1947</v>
       </c>
@@ -25186,8 +26267,11 @@
       <c r="N355" s="3" t="s">
         <v>1952</v>
       </c>
-    </row>
-    <row r="356" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O355" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="48" t="s">
         <v>1953</v>
       </c>
@@ -25230,8 +26314,11 @@
       <c r="N356" s="3" t="s">
         <v>1958</v>
       </c>
-    </row>
-    <row r="357" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O356" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="48" t="s">
         <v>1959</v>
       </c>
@@ -25274,8 +26361,11 @@
       <c r="N357" s="4" t="s">
         <v>1963</v>
       </c>
-    </row>
-    <row r="358" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O357" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="48" t="s">
         <v>1964</v>
       </c>
@@ -25318,8 +26408,11 @@
       <c r="N358" s="3" t="s">
         <v>1532</v>
       </c>
-    </row>
-    <row r="359" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O358" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="48" t="s">
         <v>1969</v>
       </c>
@@ -25362,8 +26455,11 @@
       <c r="N359" s="4" t="s">
         <v>1974</v>
       </c>
-    </row>
-    <row r="360" spans="1:14" ht="32.25" customHeight="1">
+      <c r="O359" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="48" t="s">
         <v>1975</v>
       </c>
@@ -25406,8 +26502,11 @@
       <c r="N360" s="4" t="s">
         <v>1980</v>
       </c>
-    </row>
-    <row r="361" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O360" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="48" t="s">
         <v>1981</v>
       </c>
@@ -25450,8 +26549,11 @@
       <c r="N361" s="4" t="s">
         <v>1987</v>
       </c>
-    </row>
-    <row r="362" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O361" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="48" t="s">
         <v>1988</v>
       </c>
@@ -25494,8 +26596,11 @@
       <c r="N362" s="3" t="s">
         <v>1992</v>
       </c>
-    </row>
-    <row r="363" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O362" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="48" t="s">
         <v>1993</v>
       </c>
@@ -25538,8 +26643,11 @@
       <c r="N363" s="3" t="s">
         <v>1996</v>
       </c>
-    </row>
-    <row r="364" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O363" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="48" t="s">
         <v>1997</v>
       </c>
@@ -25582,8 +26690,11 @@
       <c r="N364" s="3" t="s">
         <v>2001</v>
       </c>
-    </row>
-    <row r="365" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O364" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="365" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="48" t="s">
         <v>2002</v>
       </c>
@@ -25626,8 +26737,11 @@
       <c r="N365" s="3" t="s">
         <v>2007</v>
       </c>
-    </row>
-    <row r="366" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O365" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="366" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="48" t="s">
         <v>2008</v>
       </c>
@@ -25670,8 +26784,11 @@
       <c r="N366" s="3" t="s">
         <v>2012</v>
       </c>
-    </row>
-    <row r="367" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O366" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="367" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="48" t="s">
         <v>2013</v>
       </c>
@@ -25714,8 +26831,11 @@
       <c r="N367" s="3" t="s">
         <v>2018</v>
       </c>
-    </row>
-    <row r="368" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O367" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="368" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="48" t="s">
         <v>2019</v>
       </c>
@@ -25758,8 +26878,11 @@
       <c r="N368" s="3" t="s">
         <v>2023</v>
       </c>
-    </row>
-    <row r="369" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O368" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="369" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="48" t="s">
         <v>2024</v>
       </c>
@@ -25802,8 +26925,11 @@
       <c r="N369" s="3" t="s">
         <v>2027</v>
       </c>
-    </row>
-    <row r="370" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O369" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="370" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="48" t="s">
         <v>2028</v>
       </c>
@@ -25846,8 +26972,11 @@
       <c r="N370" s="3" t="s">
         <v>2032</v>
       </c>
-    </row>
-    <row r="371" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O370" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="48" t="s">
         <v>2033</v>
       </c>
@@ -25890,8 +27019,11 @@
       <c r="N371" s="3" t="s">
         <v>2037</v>
       </c>
-    </row>
-    <row r="372" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O371" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="372" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="48" t="s">
         <v>2038</v>
       </c>
@@ -25934,8 +27066,11 @@
       <c r="N372" s="3" t="s">
         <v>2041</v>
       </c>
-    </row>
-    <row r="373" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O372" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="373" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="48" t="s">
         <v>2042</v>
       </c>
@@ -25978,8 +27113,11 @@
       <c r="N373" s="3" t="s">
         <v>2046</v>
       </c>
-    </row>
-    <row r="374" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O373" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="374" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="48" t="s">
         <v>2047</v>
       </c>
@@ -26022,8 +27160,11 @@
       <c r="N374" s="3" t="s">
         <v>2050</v>
       </c>
-    </row>
-    <row r="375" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O374" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="375" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="48" t="s">
         <v>2051</v>
       </c>
@@ -26066,8 +27207,11 @@
       <c r="N375" s="3" t="s">
         <v>2055</v>
       </c>
-    </row>
-    <row r="376" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O375" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="376" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="48" t="s">
         <v>2056</v>
       </c>
@@ -26110,8 +27254,11 @@
       <c r="N376" s="3" t="s">
         <v>2060</v>
       </c>
-    </row>
-    <row r="377" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O376" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="48" t="s">
         <v>2061</v>
       </c>
@@ -26154,8 +27301,11 @@
       <c r="N377" s="3" t="s">
         <v>2065</v>
       </c>
-    </row>
-    <row r="378" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O377" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="48" t="s">
         <v>2066</v>
       </c>
@@ -26198,8 +27348,11 @@
       <c r="N378" s="3" t="s">
         <v>2071</v>
       </c>
-    </row>
-    <row r="379" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O378" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="48" t="s">
         <v>2072</v>
       </c>
@@ -26242,8 +27395,11 @@
       <c r="N379" s="3" t="s">
         <v>2076</v>
       </c>
-    </row>
-    <row r="380" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O379" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="48" t="s">
         <v>2077</v>
       </c>
@@ -26286,8 +27442,11 @@
       <c r="N380" s="3" t="s">
         <v>2082</v>
       </c>
-    </row>
-    <row r="381" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O380" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="48" t="s">
         <v>2083</v>
       </c>
@@ -26330,8 +27489,11 @@
       <c r="N381" s="3" t="s">
         <v>2087</v>
       </c>
-    </row>
-    <row r="382" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O381" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="382" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="48" t="s">
         <v>2088</v>
       </c>
@@ -26374,8 +27536,11 @@
       <c r="N382" s="3" t="s">
         <v>2093</v>
       </c>
-    </row>
-    <row r="383" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O382" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="383" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="48" t="s">
         <v>2094</v>
       </c>
@@ -26418,8 +27583,11 @@
       <c r="N383" s="3" t="s">
         <v>2098</v>
       </c>
-    </row>
-    <row r="384" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O383" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="48" t="s">
         <v>2099</v>
       </c>
@@ -26462,8 +27630,11 @@
       <c r="N384" s="21" t="s">
         <v>2103</v>
       </c>
-    </row>
-    <row r="385" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O384" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="48" t="s">
         <v>2104</v>
       </c>
@@ -26506,8 +27677,11 @@
       <c r="N385" s="3" t="s">
         <v>2109</v>
       </c>
-    </row>
-    <row r="386" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O385" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="386" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="48" t="s">
         <v>2110</v>
       </c>
@@ -26550,8 +27724,11 @@
       <c r="N386" s="3" t="s">
         <v>2114</v>
       </c>
-    </row>
-    <row r="387" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O386" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="387" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="48" t="s">
         <v>2115</v>
       </c>
@@ -26594,8 +27771,11 @@
       <c r="N387" s="3" t="s">
         <v>2120</v>
       </c>
-    </row>
-    <row r="388" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O387" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="388" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="48" t="s">
         <v>2121</v>
       </c>
@@ -26638,8 +27818,11 @@
       <c r="N388" s="3" t="s">
         <v>2125</v>
       </c>
-    </row>
-    <row r="389" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O388" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="389" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="48" t="s">
         <v>2126</v>
       </c>
@@ -26682,8 +27865,11 @@
       <c r="N389" s="3" t="s">
         <v>2130</v>
       </c>
-    </row>
-    <row r="390" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O389" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="48" t="s">
         <v>2131</v>
       </c>
@@ -26726,8 +27912,11 @@
       <c r="N390" s="3" t="s">
         <v>2136</v>
       </c>
-    </row>
-    <row r="391" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O390" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="391" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="48" t="s">
         <v>2137</v>
       </c>
@@ -26770,8 +27959,11 @@
       <c r="N391" s="3" t="s">
         <v>2142</v>
       </c>
-    </row>
-    <row r="392" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O391" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="48" t="s">
         <v>2143</v>
       </c>
@@ -26814,8 +28006,11 @@
       <c r="N392" s="3" t="s">
         <v>2148</v>
       </c>
-    </row>
-    <row r="393" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O392" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="393" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="48" t="s">
         <v>2149</v>
       </c>
@@ -26858,8 +28053,11 @@
       <c r="N393" s="3" t="s">
         <v>2154</v>
       </c>
-    </row>
-    <row r="394" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O393" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="48" t="s">
         <v>2155</v>
       </c>
@@ -26902,8 +28100,11 @@
       <c r="N394" s="3" t="s">
         <v>2159</v>
       </c>
-    </row>
-    <row r="395" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O394" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="395" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="48" t="s">
         <v>2160</v>
       </c>
@@ -26946,8 +28147,11 @@
       <c r="N395" s="3" t="s">
         <v>2164</v>
       </c>
-    </row>
-    <row r="396" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O395" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="396" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="48" t="s">
         <v>2165</v>
       </c>
@@ -26990,8 +28194,11 @@
       <c r="N396" s="3" t="s">
         <v>2169</v>
       </c>
-    </row>
-    <row r="397" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O396" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="397" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="48" t="s">
         <v>2170</v>
       </c>
@@ -27034,8 +28241,11 @@
       <c r="N397" s="3" t="s">
         <v>2174</v>
       </c>
-    </row>
-    <row r="398" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O397" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="48" t="s">
         <v>2175</v>
       </c>
@@ -27078,8 +28288,11 @@
       <c r="N398" s="3" t="s">
         <v>2178</v>
       </c>
-    </row>
-    <row r="399" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O398" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="399" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="48" t="s">
         <v>2179</v>
       </c>
@@ -27122,8 +28335,11 @@
       <c r="N399" s="3" t="s">
         <v>2184</v>
       </c>
-    </row>
-    <row r="400" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O399" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="400" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="48" t="s">
         <v>2185</v>
       </c>
@@ -27166,8 +28382,11 @@
       <c r="N400" s="3" t="s">
         <v>2189</v>
       </c>
-    </row>
-    <row r="401" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O400" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="401" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="48" t="s">
         <v>2190</v>
       </c>
@@ -27210,8 +28429,11 @@
       <c r="N401" s="3" t="s">
         <v>2194</v>
       </c>
-    </row>
-    <row r="402" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O401" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="402" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="48" t="s">
         <v>2195</v>
       </c>
@@ -27254,8 +28476,11 @@
       <c r="N402" s="3" t="s">
         <v>2194</v>
       </c>
-    </row>
-    <row r="403" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O402" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="403" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="48" t="s">
         <v>2199</v>
       </c>
@@ -27298,8 +28523,11 @@
       <c r="N403" s="3" t="s">
         <v>2203</v>
       </c>
-    </row>
-    <row r="404" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O403" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="404" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="48" t="s">
         <v>2204</v>
       </c>
@@ -27342,8 +28570,11 @@
       <c r="N404" s="3" t="s">
         <v>2209</v>
       </c>
-    </row>
-    <row r="405" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O404" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="405" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="48" t="s">
         <v>2210</v>
       </c>
@@ -27386,8 +28617,11 @@
       <c r="N405" s="3" t="s">
         <v>2214</v>
       </c>
-    </row>
-    <row r="406" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O405" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="406" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="48" t="s">
         <v>2215</v>
       </c>
@@ -27430,8 +28664,11 @@
       <c r="N406" s="3" t="s">
         <v>2219</v>
       </c>
-    </row>
-    <row r="407" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O406" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="407" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="48" t="s">
         <v>2220</v>
       </c>
@@ -27474,8 +28711,11 @@
       <c r="N407" s="3" t="s">
         <v>2225</v>
       </c>
-    </row>
-    <row r="408" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O407" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="408" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="48" t="s">
         <v>2226</v>
       </c>
@@ -27518,8 +28758,11 @@
       <c r="N408" s="3" t="s">
         <v>2231</v>
       </c>
-    </row>
-    <row r="409" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O408" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="409" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="48" t="s">
         <v>2232</v>
       </c>
@@ -27562,8 +28805,11 @@
       <c r="N409" s="3" t="s">
         <v>2236</v>
       </c>
-    </row>
-    <row r="410" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O409" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="410" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="48" t="s">
         <v>2237</v>
       </c>
@@ -27606,8 +28852,11 @@
       <c r="N410" s="3" t="s">
         <v>2240</v>
       </c>
-    </row>
-    <row r="411" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O410" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="411" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="48" t="s">
         <v>2241</v>
       </c>
@@ -27650,8 +28899,11 @@
       <c r="N411" s="3" t="s">
         <v>2245</v>
       </c>
-    </row>
-    <row r="412" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O411" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="412" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="48" t="s">
         <v>2246</v>
       </c>
@@ -27694,8 +28946,11 @@
       <c r="N412" s="3" t="s">
         <v>2249</v>
       </c>
-    </row>
-    <row r="413" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O412" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="413" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="48" t="s">
         <v>2250</v>
       </c>
@@ -27738,8 +28993,11 @@
       <c r="N413" s="3" t="s">
         <v>2253</v>
       </c>
-    </row>
-    <row r="414" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O413" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="414" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="48" t="s">
         <v>2254</v>
       </c>
@@ -27782,8 +29040,11 @@
       <c r="N414" s="3" t="s">
         <v>2258</v>
       </c>
-    </row>
-    <row r="415" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O414" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="415" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="48" t="s">
         <v>2259</v>
       </c>
@@ -27826,8 +29087,11 @@
       <c r="N415" s="3" t="s">
         <v>2263</v>
       </c>
-    </row>
-    <row r="416" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O415" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="416" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="48" t="s">
         <v>2264</v>
       </c>
@@ -27870,8 +29134,11 @@
       <c r="N416" s="3" t="s">
         <v>2268</v>
       </c>
-    </row>
-    <row r="417" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O416" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="417" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="48" t="s">
         <v>2269</v>
       </c>
@@ -27914,8 +29181,11 @@
       <c r="N417" s="3" t="s">
         <v>2273</v>
       </c>
-    </row>
-    <row r="418" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O417" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="418" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="48" t="s">
         <v>2274</v>
       </c>
@@ -27958,8 +29228,11 @@
       <c r="N418" s="3" t="s">
         <v>2279</v>
       </c>
-    </row>
-    <row r="419" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O418" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="419" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="48" t="s">
         <v>2280</v>
       </c>
@@ -28002,8 +29275,11 @@
       <c r="N419" s="3" t="s">
         <v>2284</v>
       </c>
-    </row>
-    <row r="420" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O419" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="48" t="s">
         <v>2285</v>
       </c>
@@ -28046,8 +29322,11 @@
       <c r="N420" s="3" t="s">
         <v>2290</v>
       </c>
-    </row>
-    <row r="421" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O420" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="421" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="48" t="s">
         <v>2291</v>
       </c>
@@ -28090,8 +29369,11 @@
       <c r="N421" s="3" t="s">
         <v>2295</v>
       </c>
-    </row>
-    <row r="422" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O421" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="422" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="48" t="s">
         <v>2296</v>
       </c>
@@ -28134,8 +29416,11 @@
       <c r="N422" s="3" t="s">
         <v>2302</v>
       </c>
-    </row>
-    <row r="423" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O422" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="423" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="48" t="s">
         <v>2303</v>
       </c>
@@ -28178,8 +29463,11 @@
       <c r="N423" s="39" t="s">
         <v>2308</v>
       </c>
-    </row>
-    <row r="424" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O423" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="424" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="49" t="s">
         <v>2309</v>
       </c>
@@ -28222,8 +29510,11 @@
       <c r="N424" s="34" t="s">
         <v>2313</v>
       </c>
-    </row>
-    <row r="425" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O424" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="425" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="48" t="s">
         <v>2314</v>
       </c>
@@ -28266,8 +29557,11 @@
       <c r="N425" s="3" t="s">
         <v>2317</v>
       </c>
-    </row>
-    <row r="426" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O425" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="48" t="s">
         <v>2318</v>
       </c>
@@ -28310,8 +29604,11 @@
       <c r="N426" s="3" t="s">
         <v>2323</v>
       </c>
-    </row>
-    <row r="427" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O426" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="427" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="48" t="s">
         <v>2324</v>
       </c>
@@ -28354,8 +29651,11 @@
       <c r="N427" s="3" t="s">
         <v>2327</v>
       </c>
-    </row>
-    <row r="428" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O427" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="428" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="48" t="s">
         <v>2328</v>
       </c>
@@ -28398,8 +29698,11 @@
       <c r="N428" s="3" t="s">
         <v>2331</v>
       </c>
-    </row>
-    <row r="429" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O428" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="429" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="57" t="s">
         <v>2332</v>
       </c>
@@ -28438,8 +29741,11 @@
         <v>140</v>
       </c>
       <c r="N429" s="10"/>
-    </row>
-    <row r="430" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O429" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="48" t="s">
         <v>2337</v>
       </c>
@@ -28482,8 +29788,11 @@
       <c r="N430" s="3" t="s">
         <v>2342</v>
       </c>
-    </row>
-    <row r="431" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O430" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="431" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="48" t="s">
         <v>2343</v>
       </c>
@@ -28526,8 +29835,11 @@
       <c r="N431" s="3" t="s">
         <v>2347</v>
       </c>
-    </row>
-    <row r="432" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O431" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="432" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="48" t="s">
         <v>2348</v>
       </c>
@@ -28570,8 +29882,11 @@
       <c r="N432" s="3" t="s">
         <v>2352</v>
       </c>
-    </row>
-    <row r="433" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O432" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="433" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="48" t="s">
         <v>2353</v>
       </c>
@@ -28614,8 +29929,11 @@
       <c r="N433" s="4" t="s">
         <v>2358</v>
       </c>
-    </row>
-    <row r="434" spans="1:14" s="43" customFormat="1" ht="24.75" customHeight="1">
+      <c r="O433" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="434" spans="1:15" s="43" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="48" t="s">
         <v>2359</v>
       </c>
@@ -28658,8 +29976,11 @@
       <c r="N434" s="4" t="s">
         <v>2365</v>
       </c>
-    </row>
-    <row r="435" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O434" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="435" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="48" t="s">
         <v>2366</v>
       </c>
@@ -28702,8 +30023,11 @@
       <c r="N435" s="2" t="s">
         <v>2370</v>
       </c>
-    </row>
-    <row r="436" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O435" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="436" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="48" t="s">
         <v>2371</v>
       </c>
@@ -28746,8 +30070,11 @@
       <c r="N436" s="2" t="s">
         <v>2375</v>
       </c>
-    </row>
-    <row r="437" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O436" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="437" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="53" t="s">
         <v>2376</v>
       </c>
@@ -28786,8 +30113,11 @@
         <v>61</v>
       </c>
       <c r="N437" s="10"/>
-    </row>
-    <row r="438" spans="1:14" ht="51" customHeight="1">
+      <c r="O437" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="438" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="58" t="s">
         <v>2381</v>
       </c>
@@ -28830,8 +30160,11 @@
       <c r="N438" s="2" t="s">
         <v>2387</v>
       </c>
-    </row>
-    <row r="439" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O438" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="439" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="58" t="s">
         <v>2388</v>
       </c>
@@ -28874,8 +30207,11 @@
       <c r="N439" s="39" t="s">
         <v>2394</v>
       </c>
-    </row>
-    <row r="440" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O439" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="440" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="53" t="s">
         <v>2395</v>
       </c>
@@ -28914,8 +30250,11 @@
         <v>24</v>
       </c>
       <c r="N440" s="10"/>
-    </row>
-    <row r="441" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O440" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="441" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="53" t="s">
         <v>2398</v>
       </c>
@@ -28954,8 +30293,11 @@
         <v>50</v>
       </c>
       <c r="N441" s="10"/>
-    </row>
-    <row r="442" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O441" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="442" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="53" t="s">
         <v>2402</v>
       </c>
@@ -28994,8 +30336,11 @@
         <v>50</v>
       </c>
       <c r="N442" s="10"/>
-    </row>
-    <row r="443" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O442" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="443" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="53" t="s">
         <v>2406</v>
       </c>
@@ -29034,8 +30379,11 @@
         <v>50</v>
       </c>
       <c r="N443" s="10"/>
-    </row>
-    <row r="444" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O443" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="444" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="53" t="s">
         <v>2409</v>
       </c>
@@ -29074,8 +30422,11 @@
         <v>50</v>
       </c>
       <c r="N444" s="10"/>
-    </row>
-    <row r="445" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O444" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="445" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="53" t="s">
         <v>2415</v>
       </c>
@@ -29114,8 +30465,11 @@
         <v>50</v>
       </c>
       <c r="N445" s="10"/>
-    </row>
-    <row r="446" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O445" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="446" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="53" t="s">
         <v>2420</v>
       </c>
@@ -29154,8 +30508,11 @@
         <v>50</v>
       </c>
       <c r="N446" s="10"/>
-    </row>
-    <row r="447" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O446" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="447" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="53" t="s">
         <v>2424</v>
       </c>
@@ -29194,8 +30551,11 @@
         <v>50</v>
       </c>
       <c r="N447" s="10"/>
-    </row>
-    <row r="448" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O447" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="53" t="s">
         <v>2428</v>
       </c>
@@ -29234,8 +30594,11 @@
         <v>61</v>
       </c>
       <c r="N448" s="10"/>
-    </row>
-    <row r="449" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O448" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="58" t="s">
         <v>2432</v>
       </c>
@@ -29278,8 +30641,11 @@
       <c r="N449" s="4" t="s">
         <v>2438</v>
       </c>
-    </row>
-    <row r="450" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O449" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="450" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="53" t="s">
         <v>2439</v>
       </c>
@@ -29318,8 +30684,11 @@
         <v>24</v>
       </c>
       <c r="N450" s="10"/>
-    </row>
-    <row r="451" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O450" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="53" t="s">
         <v>2443</v>
       </c>
@@ -29358,8 +30727,11 @@
         <v>41</v>
       </c>
       <c r="N451" s="10"/>
-    </row>
-    <row r="452" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O451" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="452" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="53" t="s">
         <v>2447</v>
       </c>
@@ -29398,8 +30770,11 @@
         <v>50</v>
       </c>
       <c r="N452" s="10"/>
-    </row>
-    <row r="453" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O452" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="453" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="53" t="s">
         <v>2452</v>
       </c>
@@ -29438,8 +30813,11 @@
         <v>24</v>
       </c>
       <c r="N453" s="10"/>
-    </row>
-    <row r="454" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O453" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="454" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="53" t="s">
         <v>2454</v>
       </c>
@@ -29478,8 +30856,11 @@
         <v>50</v>
       </c>
       <c r="N454" s="10"/>
-    </row>
-    <row r="455" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O454" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="455" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="53" t="s">
         <v>2458</v>
       </c>
@@ -29518,8 +30899,11 @@
         <v>50</v>
       </c>
       <c r="N455" s="10"/>
-    </row>
-    <row r="456" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O455" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="456" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="53" t="s">
         <v>2459</v>
       </c>
@@ -29558,8 +30942,11 @@
         <v>41</v>
       </c>
       <c r="N456" s="10"/>
-    </row>
-    <row r="457" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O456" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="457" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="53" t="s">
         <v>2462</v>
       </c>
@@ -29598,8 +30985,11 @@
         <v>61</v>
       </c>
       <c r="N457" s="10"/>
-    </row>
-    <row r="458" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O457" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="458" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="53" t="s">
         <v>2467</v>
       </c>
@@ -29638,8 +31028,11 @@
         <v>41</v>
       </c>
       <c r="N458" s="10"/>
-    </row>
-    <row r="459" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O458" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="459" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="53" t="s">
         <v>2471</v>
       </c>
@@ -29678,8 +31071,11 @@
         <v>61</v>
       </c>
       <c r="N459" s="10"/>
-    </row>
-    <row r="460" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O459" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="53" t="s">
         <v>2475</v>
       </c>
@@ -29718,8 +31114,11 @@
         <v>24</v>
       </c>
       <c r="N460" s="10"/>
-    </row>
-    <row r="461" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O460" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="461" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="53" t="s">
         <v>2478</v>
       </c>
@@ -29758,8 +31157,11 @@
         <v>50</v>
       </c>
       <c r="N461" s="10"/>
-    </row>
-    <row r="462" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O461" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="462" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="53" t="s">
         <v>2482</v>
       </c>
@@ -29798,8 +31200,11 @@
         <v>24</v>
       </c>
       <c r="N462" s="10"/>
-    </row>
-    <row r="463" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O462" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="463" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="53" t="s">
         <v>2483</v>
       </c>
@@ -29838,8 +31243,11 @@
         <v>140</v>
       </c>
       <c r="N463" s="10"/>
-    </row>
-    <row r="464" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O463" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="464" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="53" t="s">
         <v>2488</v>
       </c>
@@ -29878,8 +31286,11 @@
         <v>50</v>
       </c>
       <c r="N464" s="10"/>
-    </row>
-    <row r="465" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O464" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="465" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="53" t="s">
         <v>2493</v>
       </c>
@@ -29918,8 +31329,11 @@
         <v>50</v>
       </c>
       <c r="N465" s="10"/>
-    </row>
-    <row r="466" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O465" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="466" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="53" t="s">
         <v>2497</v>
       </c>
@@ -29958,8 +31372,11 @@
         <v>140</v>
       </c>
       <c r="N466" s="10"/>
-    </row>
-    <row r="467" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O466" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="467" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="53" t="s">
         <v>2499</v>
       </c>
@@ -29998,8 +31415,11 @@
         <v>50</v>
       </c>
       <c r="N467" s="10"/>
-    </row>
-    <row r="468" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O467" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="468" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="53" t="s">
         <v>2503</v>
       </c>
@@ -30038,8 +31458,11 @@
         <v>50</v>
       </c>
       <c r="N468" s="10"/>
-    </row>
-    <row r="469" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O468" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="469" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="53" t="s">
         <v>2507</v>
       </c>
@@ -30078,8 +31501,11 @@
         <v>50</v>
       </c>
       <c r="N469" s="10"/>
-    </row>
-    <row r="470" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O469" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="470" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="53" t="s">
         <v>2510</v>
       </c>
@@ -30118,8 +31544,11 @@
         <v>50</v>
       </c>
       <c r="N470" s="10"/>
-    </row>
-    <row r="471" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O470" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="53" t="s">
         <v>2512</v>
       </c>
@@ -30158,8 +31587,11 @@
         <v>41</v>
       </c>
       <c r="N471" s="10"/>
-    </row>
-    <row r="472" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O471" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="472" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="53" t="s">
         <v>2514</v>
       </c>
@@ -30198,8 +31630,11 @@
         <v>140</v>
       </c>
       <c r="N472" s="10"/>
-    </row>
-    <row r="473" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O472" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="473" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="53" t="s">
         <v>2519</v>
       </c>
@@ -30238,8 +31673,11 @@
         <v>41</v>
       </c>
       <c r="N473" s="10"/>
-    </row>
-    <row r="474" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O473" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="53" t="s">
         <v>2523</v>
       </c>
@@ -30278,8 +31716,11 @@
         <v>61</v>
       </c>
       <c r="N474" s="10"/>
-    </row>
-    <row r="475" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O474" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="475" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="53" t="s">
         <v>2527</v>
       </c>
@@ -30318,8 +31759,11 @@
         <v>41</v>
       </c>
       <c r="N475" s="10"/>
-    </row>
-    <row r="476" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O475" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="53" t="s">
         <v>2531</v>
       </c>
@@ -30358,8 +31802,11 @@
         <v>24</v>
       </c>
       <c r="N476" s="10"/>
-    </row>
-    <row r="477" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O476" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="477" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="53" t="s">
         <v>2533</v>
       </c>
@@ -30398,8 +31845,11 @@
         <v>50</v>
       </c>
       <c r="N477" s="10"/>
-    </row>
-    <row r="478" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O477" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="53" t="s">
         <v>2534</v>
       </c>
@@ -30438,8 +31888,11 @@
         <v>50</v>
       </c>
       <c r="N478" s="10"/>
-    </row>
-    <row r="479" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O478" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="479" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="53" t="s">
         <v>2535</v>
       </c>
@@ -30478,8 +31931,11 @@
         <v>41</v>
       </c>
       <c r="N479" s="10"/>
-    </row>
-    <row r="480" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O479" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="53" t="s">
         <v>2537</v>
       </c>
@@ -30518,8 +31974,11 @@
         <v>50</v>
       </c>
       <c r="N480" s="10"/>
-    </row>
-    <row r="481" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O480" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="481" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="53" t="s">
         <v>2541</v>
       </c>
@@ -30558,8 +32017,11 @@
         <v>50</v>
       </c>
       <c r="N481" s="10"/>
-    </row>
-    <row r="482" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O481" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="482" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="53" t="s">
         <v>2542</v>
       </c>
@@ -30598,8 +32060,11 @@
         <v>41</v>
       </c>
       <c r="N482" s="10"/>
-    </row>
-    <row r="483" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O482" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="483" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="53" t="s">
         <v>2544</v>
       </c>
@@ -30638,8 +32103,11 @@
         <v>50</v>
       </c>
       <c r="N483" s="10"/>
-    </row>
-    <row r="484" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O483" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="53" t="s">
         <v>2547</v>
       </c>
@@ -30678,8 +32146,11 @@
         <v>61</v>
       </c>
       <c r="N484" s="10"/>
-    </row>
-    <row r="485" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O484" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="485" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="53" t="s">
         <v>2552</v>
       </c>
@@ -30718,8 +32189,11 @@
         <v>140</v>
       </c>
       <c r="N485" s="10"/>
-    </row>
-    <row r="486" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O485" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="53" t="s">
         <v>2556</v>
       </c>
@@ -30758,8 +32232,11 @@
         <v>140</v>
       </c>
       <c r="N486" s="10"/>
-    </row>
-    <row r="487" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O486" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="53" t="s">
         <v>2557</v>
       </c>
@@ -30798,8 +32275,11 @@
         <v>61</v>
       </c>
       <c r="N487" s="10"/>
-    </row>
-    <row r="488" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O487" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="53" t="s">
         <v>2561</v>
       </c>
@@ -30838,8 +32318,11 @@
         <v>41</v>
       </c>
       <c r="N488" s="10"/>
-    </row>
-    <row r="489" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O488" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="53" t="s">
         <v>2564</v>
       </c>
@@ -30878,8 +32361,11 @@
         <v>50</v>
       </c>
       <c r="N489" s="10"/>
-    </row>
-    <row r="490" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O489" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="490" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="53" t="s">
         <v>2567</v>
       </c>
@@ -30918,8 +32404,11 @@
         <v>41</v>
       </c>
       <c r="N490" s="10"/>
-    </row>
-    <row r="491" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O490" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="491" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="53" t="s">
         <v>2570</v>
       </c>
@@ -30958,8 +32447,11 @@
         <v>50</v>
       </c>
       <c r="N491" s="10"/>
-    </row>
-    <row r="492" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O491" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="492" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="53" t="s">
         <v>2574</v>
       </c>
@@ -30998,8 +32490,11 @@
         <v>61</v>
       </c>
       <c r="N492" s="10"/>
-    </row>
-    <row r="493" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O492" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="493" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="53" t="s">
         <v>2578</v>
       </c>
@@ -31038,8 +32533,11 @@
         <v>24</v>
       </c>
       <c r="N493" s="10"/>
-    </row>
-    <row r="494" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O493" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="494" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="53" t="s">
         <v>2581</v>
       </c>
@@ -31078,8 +32576,11 @@
         <v>41</v>
       </c>
       <c r="N494" s="10"/>
-    </row>
-    <row r="495" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O494" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="495" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="53" t="s">
         <v>2585</v>
       </c>
@@ -31118,8 +32619,11 @@
         <v>50</v>
       </c>
       <c r="N495" s="10"/>
-    </row>
-    <row r="496" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O495" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="53" t="s">
         <v>2589</v>
       </c>
@@ -31158,8 +32662,11 @@
         <v>24</v>
       </c>
       <c r="N496" s="10"/>
-    </row>
-    <row r="497" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O496" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="53" t="s">
         <v>2592</v>
       </c>
@@ -31198,8 +32705,11 @@
         <v>61</v>
       </c>
       <c r="N497" s="10"/>
-    </row>
-    <row r="498" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O497" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="498" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="53" t="s">
         <v>2596</v>
       </c>
@@ -31238,8 +32748,11 @@
         <v>41</v>
       </c>
       <c r="N498" s="10"/>
-    </row>
-    <row r="499" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O498" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="53" t="s">
         <v>2598</v>
       </c>
@@ -31278,8 +32791,11 @@
         <v>50</v>
       </c>
       <c r="N499" s="10"/>
-    </row>
-    <row r="500" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O499" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="53" t="s">
         <v>2603</v>
       </c>
@@ -31318,8 +32834,11 @@
         <v>24</v>
       </c>
       <c r="N500" s="10"/>
-    </row>
-    <row r="501" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O500" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="53" t="s">
         <v>2608</v>
       </c>
@@ -31358,8 +32877,11 @@
         <v>50</v>
       </c>
       <c r="N501" s="10"/>
-    </row>
-    <row r="502" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O501" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="53" t="s">
         <v>2613</v>
       </c>
@@ -31398,8 +32920,11 @@
         <v>61</v>
       </c>
       <c r="N502" s="10"/>
-    </row>
-    <row r="503" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O502" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="503" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="53" t="s">
         <v>2614</v>
       </c>
@@ -31438,8 +32963,11 @@
         <v>24</v>
       </c>
       <c r="N503" s="10"/>
-    </row>
-    <row r="504" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O503" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="53" t="s">
         <v>2617</v>
       </c>
@@ -31478,8 +33006,11 @@
         <v>50</v>
       </c>
       <c r="N504" s="10"/>
-    </row>
-    <row r="505" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O504" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="53" t="s">
         <v>2620</v>
       </c>
@@ -31518,8 +33049,11 @@
         <v>50</v>
       </c>
       <c r="N505" s="10"/>
-    </row>
-    <row r="506" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O505" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="53" t="s">
         <v>2623</v>
       </c>
@@ -31558,8 +33092,11 @@
         <v>140</v>
       </c>
       <c r="N506" s="10"/>
-    </row>
-    <row r="507" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O506" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="507" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="53" t="s">
         <v>2625</v>
       </c>
@@ -31598,8 +33135,11 @@
         <v>41</v>
       </c>
       <c r="N507" s="10"/>
-    </row>
-    <row r="508" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O507" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="53" t="s">
         <v>2628</v>
       </c>
@@ -31638,8 +33178,11 @@
         <v>24</v>
       </c>
       <c r="N508" s="10"/>
-    </row>
-    <row r="509" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O508" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="509" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="53" t="s">
         <v>2632</v>
       </c>
@@ -31678,8 +33221,11 @@
         <v>24</v>
       </c>
       <c r="N509" s="10"/>
-    </row>
-    <row r="510" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O509" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="53" t="s">
         <v>2636</v>
       </c>
@@ -31718,8 +33264,11 @@
         <v>24</v>
       </c>
       <c r="N510" s="10"/>
-    </row>
-    <row r="511" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O510" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="53" t="s">
         <v>2640</v>
       </c>
@@ -31758,8 +33307,11 @@
         <v>50</v>
       </c>
       <c r="N511" s="10"/>
-    </row>
-    <row r="512" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O511" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="53" t="s">
         <v>2643</v>
       </c>
@@ -31798,8 +33350,11 @@
         <v>24</v>
       </c>
       <c r="N512" s="10"/>
-    </row>
-    <row r="513" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O512" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="513" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="53" t="s">
         <v>2646</v>
       </c>
@@ -31838,8 +33393,11 @@
         <v>50</v>
       </c>
       <c r="N513" s="10"/>
-    </row>
-    <row r="514" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O513" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="53" t="s">
         <v>2650</v>
       </c>
@@ -31878,8 +33436,11 @@
         <v>50</v>
       </c>
       <c r="N514" s="10"/>
-    </row>
-    <row r="515" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O514" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="58" t="s">
         <v>2654</v>
       </c>
@@ -31922,8 +33483,11 @@
       <c r="N515" s="4" t="s">
         <v>2660</v>
       </c>
-    </row>
-    <row r="516" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O515" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="53" t="s">
         <v>2661</v>
       </c>
@@ -31962,8 +33526,11 @@
         <v>41</v>
       </c>
       <c r="N516" s="10"/>
-    </row>
-    <row r="517" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O516" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="53" t="s">
         <v>2665</v>
       </c>
@@ -32002,8 +33569,11 @@
         <v>41</v>
       </c>
       <c r="N517" s="10"/>
-    </row>
-    <row r="518" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O517" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="53" t="s">
         <v>2668</v>
       </c>
@@ -32042,8 +33612,11 @@
         <v>50</v>
       </c>
       <c r="N518" s="10"/>
-    </row>
-    <row r="519" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O518" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="53" t="s">
         <v>2671</v>
       </c>
@@ -32082,8 +33655,11 @@
         <v>50</v>
       </c>
       <c r="N519" s="10"/>
-    </row>
-    <row r="520" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O519" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="53" t="s">
         <v>2672</v>
       </c>
@@ -32122,8 +33698,11 @@
         <v>41</v>
       </c>
       <c r="N520" s="10"/>
-    </row>
-    <row r="521" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O520" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="53" t="s">
         <v>2674</v>
       </c>
@@ -32162,8 +33741,11 @@
         <v>50</v>
       </c>
       <c r="N521" s="10"/>
-    </row>
-    <row r="522" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O521" s="63" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="53" t="s">
         <v>2678</v>
       </c>
@@ -32202,8 +33784,11 @@
         <v>50</v>
       </c>
       <c r="N522" s="10"/>
-    </row>
-    <row r="523" spans="1:14" ht="24.75" customHeight="1">
+      <c r="O522" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="55" t="s">
         <v>2679</v>
       </c>
@@ -32242,10 +33827,13 @@
         <v>50</v>
       </c>
       <c r="N523" s="10"/>
+      <c r="O523" s="63" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:A431">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H323" r:id="rId1" xr:uid="{A7481355-A0D8-4A4C-8886-035E98647298}"/>
@@ -32693,15 +34281,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004A88CC3DB4BEF140836682561FF1A3EC" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="8de4f70edb2c6e64a148c9a75f32db1a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="be150ef9-4f9c-441d-8ced-c7d491dd0c3d" xmlns:ns3="402ced5c-caaa-4c89-aae2-d6c39e84cf9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="75ce5bf2351aa702a81a52d685efe923" ns2:_="" ns3:_="">
     <xsd:import namespace="be150ef9-4f9c-441d-8ced-c7d491dd0c3d"/>
@@ -32958,6 +34537,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -32972,13 +34560,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D608A46-4C6F-43D5-B0C8-585FFBF6B4F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C026806-D5E5-4453-9325-C089BC360E85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="be150ef9-4f9c-441d-8ced-c7d491dd0c3d"/>
+    <ds:schemaRef ds:uri="402ced5c-caaa-4c89-aae2-d6c39e84cf9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C026806-D5E5-4453-9325-C089BC360E85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D608A46-4C6F-43D5-B0C8-585FFBF6B4F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E0FC2A7-2894-4F5B-B3B7-6F6BB9EC858E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E0FC2A7-2894-4F5B-B3B7-6F6BB9EC858E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="402ced5c-caaa-4c89-aae2-d6c39e84cf9c"/>
+    <ds:schemaRef ds:uri="be150ef9-4f9c-441d-8ced-c7d491dd0c3d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>